--- a/order_forms/034_snack_bar_product_replenishment_order_form--order_forms.xlsx
+++ b/order_forms/034_snack_bar_product_replenishment_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>select_one_email</t>
+          <t>select_one_email_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Select One Email</t>
+          <t>Select One Email 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>select_multiple_emails</t>
+          <t>select_multiple_emails_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Select Multiple Emails</t>
+          <t>Select Multiple Emails 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>select_one_phone</t>
+          <t>select_one_phone_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Select One Phone</t>
+          <t>Select One Phone 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>select_multiple_phones</t>
+          <t>select_multiple_phones_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Select Multiple Phones</t>
+          <t>Select Multiple Phones 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_one_email_choices</t>
+          <t>select_one_email_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>select_one_email_choices</t>
+          <t>select_one_email_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1682,7 +1682,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_multiple_emails_choices</t>
+          <t>select_multiple_emails_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>select_multiple_emails_choices</t>
+          <t>select_multiple_emails_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1716,7 +1716,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_one_phone_choices</t>
+          <t>select_one_phone_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>select_one_phone_choices</t>
+          <t>select_one_phone_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1750,7 +1750,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>select_multiple_phones_choices</t>
+          <t>select_multiple_phones_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1767,7 +1767,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>select_multiple_phones_choices</t>
+          <t>select_multiple_phones_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
